--- a/SVI_NFT_R/SEQUENCE/Main/00_EqToEq/SDV Gamma Foldable Line/GeneratedSource/DataBlocks/EqToEq/EqToEq.LowerToSelf.Bits.xlsx
+++ b/SVI_NFT_R/SEQUENCE/Main/00_EqToEq/SDV Gamma Foldable Line/GeneratedSource/DataBlocks/EqToEq/EqToEq.LowerToSelf.Bits.xlsx
@@ -1,24 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01.Project\2025\E2508A-113~115 SDV 박닌 V3 NFT SVI-M 대응(2Cell)\Application\Source\SVI_NFT_F\SVI_NFT_F\SEQUENCE\Main\00_EqToEq\SDV Gamma Foldable Line\GeneratedSource\DataBlocks\EqToEq\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\01. ENC\02_Samsung\08_V34F_NFT\01_Program\SVI_NFT_R_Type3_55-60_nguyen\SVI_NFT_R\SVI_NFT_R\SEQUENCE\Main\00_EqToEq\SDV Gamma Foldable Line\GeneratedSource\DataBlocks\EqToEq\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE46686-A72E-446B-ACC7-7F0F317B3E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12285"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Map" sheetId="1" r:id="rId1"/>
     <sheet name="Define" sheetId="4" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -187,30 +199,28 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ReceiveVacuumOnP1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ReceiveVacuumOnP2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>ReceiveVacuumOffP1</t>
+  </si>
+  <si>
+    <t>ReceiveVacuumOffP2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -223,7 +233,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -254,32 +264,22 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="표준 12" xfId="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준 12" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -323,34 +323,34 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="표1_34" displayName="표1_34" ref="A1:I13" totalsRowShown="0">
-  <autoFilter ref="A1:I13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1_34" displayName="표1_34" ref="A1:I13" totalsRowShown="0">
+  <autoFilter ref="A1:I13" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="9">
-    <tableColumn id="2" name="ID"/>
-    <tableColumn id="13" name="Byte Index(or Offset)">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ID"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Byte Index(or Offset)">
       <calculatedColumnFormula>INT(M2/8)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" name="Bit Index" dataDxfId="1">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Bit Index" dataDxfId="1">
       <calculatedColumnFormula>MOD(M2,8)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" name="Handling Data Type"/>
-    <tableColumn id="8" name="Array Length"/>
-    <tableColumn id="9" name="Decimal Point"/>
-    <tableColumn id="19" name="Label">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Handling Data Type"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Array Length"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Decimal Point"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Label">
       <calculatedColumnFormula>"B"&amp;DEC2HEX(M2,4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" name="Description"/>
-    <tableColumn id="17" name="Comment" dataDxfId="0" dataCellStyle="표준 12"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Description"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Comment" dataDxfId="0" dataCellStyle="표준 12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="표1" displayName="표1" ref="A1:A15" totalsRowShown="0">
-  <autoFilter ref="A1:A15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="표1" displayName="표1" ref="A1:A15" totalsRowShown="0">
+  <autoFilter ref="A1:A15" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="1">
-    <tableColumn id="1" name="데이터 타입"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="데이터 타입"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -618,22 +618,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M13"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21.875" customWidth="1"/>
-    <col min="2" max="2" width="22.25" customWidth="1"/>
-    <col min="3" max="3" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.375" customWidth="1"/>
-    <col min="5" max="5" width="15.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.375" customWidth="1"/>
-    <col min="9" max="9" width="40.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.85546875" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.42578125" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.42578125" customWidth="1"/>
+    <col min="9" max="9" width="40.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -665,326 +665,290 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2">
         <f t="shared" ref="B2:B13" si="0">INT(M2/8)</f>
         <v>0</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2">
         <f t="shared" ref="C2:C13" si="1">MOD(M2,8)</f>
         <v>0</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1" t="str">
+      <c r="G2" t="str">
         <f>"B"&amp;DEC2HEX(M2,4)</f>
         <v>B0000</v>
       </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="2"/>
+      <c r="I2" s="1"/>
       <c r="M2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1" t="str">
+      <c r="G3" t="str">
         <f t="shared" ref="G3:G13" si="2">"B"&amp;DEC2HEX(M3,4)</f>
         <v>B0001</v>
       </c>
-      <c r="H3" s="1"/>
-      <c r="I3" s="3"/>
+      <c r="I3" s="2"/>
       <c r="M3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1" t="str">
+      <c r="G4" t="str">
         <f t="shared" si="2"/>
         <v>B0002</v>
       </c>
-      <c r="H4" s="1"/>
-      <c r="I4" s="3"/>
+      <c r="I4" s="2"/>
       <c r="M4">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:13">
+      <c r="A5" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1" t="str">
+      <c r="G5" t="str">
         <f t="shared" si="2"/>
         <v>B0003</v>
       </c>
-      <c r="H5" s="1"/>
-      <c r="I5" s="3"/>
+      <c r="I5" s="2"/>
       <c r="M5">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:13">
+      <c r="A6" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6">
         <f>INT(M6/8)</f>
         <v>0</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6">
         <f>MOD(M6,8)</f>
         <v>4</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1" t="str">
+      <c r="G6" t="str">
         <f>"B"&amp;DEC2HEX(M6,4)</f>
         <v>B0004</v>
       </c>
-      <c r="H6" s="1"/>
-      <c r="I6" s="5"/>
+      <c r="I6" s="2"/>
       <c r="M6">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:13">
+      <c r="A7" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7">
         <f>INT(M7/8)</f>
         <v>0</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7">
         <f>MOD(M7,8)</f>
         <v>5</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1" t="str">
+      <c r="G7" t="str">
         <f>"B"&amp;DEC2HEX(M7,4)</f>
         <v>B0005</v>
       </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="5"/>
+      <c r="I7" s="2"/>
       <c r="M7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:13">
+      <c r="A8" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8">
         <f>INT(M8/8)</f>
         <v>0</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8">
         <f>MOD(M8,8)</f>
         <v>6</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1" t="str">
+      <c r="G8" t="str">
         <f>"B"&amp;DEC2HEX(M8,4)</f>
         <v>B0006</v>
       </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="5"/>
+      <c r="I8" s="2"/>
       <c r="M8">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:13">
+      <c r="A9" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9">
         <f>INT(M9/8)</f>
         <v>0</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9">
         <f>MOD(M9,8)</f>
         <v>7</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1" t="str">
+      <c r="G9" t="str">
         <f>"B"&amp;DEC2HEX(M9,4)</f>
         <v>B0007</v>
       </c>
-      <c r="H9" s="1"/>
-      <c r="I9" s="5"/>
+      <c r="I9" s="2"/>
       <c r="M9">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:13">
+      <c r="A10" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10">
         <f>INT(M10/8)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10">
         <f>MOD(M10,8)</f>
         <v>5</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1" t="str">
+      <c r="G10" t="str">
         <f>"B"&amp;DEC2HEX(M10,4)</f>
         <v>B000D</v>
       </c>
-      <c r="H10" s="1"/>
-      <c r="I10" s="5"/>
+      <c r="I10" s="2"/>
       <c r="M10">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="1:13">
+      <c r="A11" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1" t="str">
+      <c r="G11" t="str">
         <f t="shared" si="2"/>
         <v>B000E</v>
       </c>
-      <c r="H11" s="1"/>
-      <c r="I11" s="3"/>
+      <c r="I11" s="2"/>
       <c r="M11">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+    <row r="12" spans="1:13">
+      <c r="A12" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1" t="str">
+      <c r="G12" t="str">
         <f t="shared" si="2"/>
         <v>B000F</v>
       </c>
-      <c r="H12" s="1"/>
-      <c r="I12" s="3"/>
+      <c r="I12" s="2"/>
       <c r="M12">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+    <row r="13" spans="1:13">
+      <c r="A13" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1" t="str">
+      <c r="G13" t="str">
         <f t="shared" si="2"/>
         <v>B001F</v>
       </c>
-      <c r="H13" s="1"/>
-      <c r="I13" s="3"/>
+      <c r="I13" s="2"/>
       <c r="M13">
         <v>31</v>
       </c>
@@ -993,28 +957,28 @@
   <dataConsolidate/>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="8">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="배열의 길이" prompt="  해당 파라미터가 공백이면 단일 데이터로 생성하고, 정수 값이 입력되면 배열 데이터로 생성합니다._x000a__x000a_유효 데이터: _x000a_  - 공백 (단일 타입)_x000a_  - 1 ~ 2147483647 (배열 타입)" sqref="E2:E13">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="배열의 길이" prompt="  해당 파라미터가 공백이면 단일 데이터로 생성하고, 정수 값이 입력되면 배열 데이터로 생성합니다._x000a__x000a_유효 데이터: _x000a_  - 공백 (단일 타입)_x000a_  - 1 ~ 2147483647 (배열 타입)" sqref="E2:E13" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="textLength" imeMode="halfAlpha" showInputMessage="1" showErrorMessage="1" promptTitle="ID (변수명)" prompt="데이터의 고유한 이름을 설정합니다._x000a__x000a_※ID는 코드 변환시 변수명으로 사용되기 때문에 C#문법에서 허용하지 않는 작명 방식은 지원하지 않음" sqref="A2:A13">
+    <dataValidation type="textLength" imeMode="halfAlpha" showInputMessage="1" showErrorMessage="1" promptTitle="ID (변수명)" prompt="데이터의 고유한 이름을 설정합니다._x000a__x000a_※ID는 코드 변환시 변수명으로 사용되기 때문에 C#문법에서 허용하지 않는 작명 방식은 지원하지 않음" sqref="A2:A13" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>1</formula1>
       <formula2>256</formula2>
     </dataValidation>
-    <dataValidation type="custom" showInputMessage="1" showErrorMessage="1" promptTitle="바이트 인덱스(or 오프셋)" prompt="  해당 데이터의 위치를 나타내는 정보를 설정합니다._x000a__x000a_유효 데이터:_x000a_- 'auto'_x000a_- 0 ~ 2147483647_x000a__x000a_※ 'auto'란?_x000a_이전 데이터가 끝난 다음 위치를 자동으로 계산해서 넣어주는 기능" sqref="B2:B13">
+    <dataValidation type="custom" showInputMessage="1" showErrorMessage="1" promptTitle="바이트 인덱스(or 오프셋)" prompt="  해당 데이터의 위치를 나타내는 정보를 설정합니다._x000a__x000a_유효 데이터:_x000a_- 'auto'_x000a_- 0 ~ 2147483647_x000a__x000a_※ 'auto'란?_x000a_이전 데이터가 끝난 다음 위치를 자동으로 계산해서 넣어주는 기능" sqref="B2:B13" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>IF(ISNUMBER(B2), AND(B2 &gt;= 0, B2 &lt; 2147483647), AND(LOWER(B2) = "auto", NOT(ISBLANK(B2))))</formula1>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="비트 인덱스" prompt="  해당 데이터의 위치를 나타내는 정보를 설정합니다._x000a__x000a_유효 데이터:_x000a_- 공백 (bool형이 선택되지 않았을 때)_x000a_- 0 ~ 7 (bool형이 선택됐을 때)_x000a__x000a_※'Bit Index'는 'Handling Data Tpye'이 'bool'로 설정됐을 때에만 적용됩니다." sqref="C2:C13">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="비트 인덱스" prompt="  해당 데이터의 위치를 나타내는 정보를 설정합니다._x000a__x000a_유효 데이터:_x000a_- 공백 (bool형이 선택되지 않았을 때)_x000a_- 0 ~ 7 (bool형이 선택됐을 때)_x000a__x000a_※'Bit Index'는 'Handling Data Tpye'이 'bool'로 설정됐을 때에만 적용됩니다." sqref="C2:C13" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>0</formula1>
       <formula2>7</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="소수점 위치" prompt="(옵션)" sqref="F2:F13">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="소수점 위치" prompt="(옵션)" sqref="F2:F13" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>0</formula1>
       <formula2>10</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="라벨" prompt="(옵션)" sqref="G2:G13"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="코맨트" prompt="(옵션)" sqref="I2:I13"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="설명" prompt="(옵션)" sqref="H2:H13"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="라벨" prompt="(옵션)" sqref="G2:G13" xr:uid="{00000000-0002-0000-0000-000005000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="코맨트" prompt="(옵션)" sqref="I2:I13" xr:uid="{00000000-0002-0000-0000-000006000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="설명" prompt="(옵션)" sqref="H2:H13" xr:uid="{00000000-0002-0000-0000-000007000000}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1024,7 +988,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" imeMode="halfAlpha" showInputMessage="1" promptTitle="데이터 타입" prompt="  해당 데이터의 타입을 설정합니다._x000a__x000a_데이터 범위:_x000a_- 사용자 정의 데이터 블록 타입_x000a_- 기본 데이터 타입(bool, byte, sbyte, ushort, short, uint, int, ulong, long, float, double, char)_x000a_">
+        <x14:dataValidation type="list" imeMode="halfAlpha" showInputMessage="1" promptTitle="데이터 타입" prompt="  해당 데이터의 타입을 설정합니다._x000a__x000a_데이터 범위:_x000a_- 사용자 정의 데이터 블록 타입_x000a_- 기본 데이터 타입(bool, byte, sbyte, ushort, short, uint, int, ulong, long, float, double, char)_x000a_" xr:uid="{00000000-0002-0000-0000-000008000000}">
           <x14:formula1>
             <xm:f>Define!$A$2:$A$15</xm:f>
           </x14:formula1>
@@ -1037,87 +1001,87 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="1"/>
   </sheetPr>
   <dimension ref="A1:A15"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.75" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1">
       <c r="A3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1">
       <c r="A4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1">
       <c r="A6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1">
       <c r="A7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1">
       <c r="A8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1">
       <c r="A9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1">
       <c r="A10" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1">
       <c r="A11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1">
       <c r="A12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1">
       <c r="A13" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1">
       <c r="A14" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1">
       <c r="A15" t="s">
         <v>21</v>
       </c>
